--- a/ARCHIVOS/EVALUADORES/BASE.xlsx
+++ b/ARCHIVOS/EVALUADORES/BASE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dashboard\ARCHIVOS\EVALUADORES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8294D71B-EB20-4E86-AA7D-EC0003C51423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B7288C-A8C3-407F-AAA4-8DF7D0597359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{CABBB291-AB3E-4F44-98DC-A2CF12E2842C}"/>
   </bookViews>
